--- a/prospection/prospection-ecoles-ia.xlsx
+++ b/prospection/prospection-ecoles-ia.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Suivi appels'!$A$1:$P$107</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Base contacts'!$A$1:$M$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Base contacts'!$A$1:$O$106</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -105,7 +105,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -130,6 +130,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -159,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -210,7 +215,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1755,11 +1763,7 @@
           <t>+225 07 08 91 46 30</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>contact@groupelasorbonne.com</t>
-        </is>
-      </c>
+      <c r="F13" s="17" t="inlineStr"/>
       <c r="G13" s="18" t="inlineStr"/>
       <c r="H13" s="18" t="inlineStr"/>
       <c r="I13" s="18" t="inlineStr">
@@ -1898,11 +1902,7 @@
           <t>+225 01 73 29 48 90</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>info@geige.ci</t>
-        </is>
-      </c>
+      <c r="F16" s="17" t="inlineStr"/>
       <c r="G16" s="18" t="inlineStr"/>
       <c r="H16" s="18" t="inlineStr"/>
       <c r="I16" s="18" t="inlineStr">
@@ -1947,11 +1947,7 @@
           <t>+225 07 59 74 39 10</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>infos24@gestpci.com</t>
-        </is>
-      </c>
+      <c r="F17" s="17" t="inlineStr"/>
       <c r="G17" s="18" t="inlineStr"/>
       <c r="H17" s="18" t="inlineStr"/>
       <c r="I17" s="18" t="inlineStr">
@@ -2333,7 +2329,7 @@
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>infos@isfmi.net</t>
+          <t>isfmiisfmi@yahoo.fr</t>
         </is>
       </c>
       <c r="G25" s="18" t="inlineStr"/>
@@ -2374,7 +2370,7 @@
       <c r="E26" s="17" t="inlineStr"/>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>iupacocody@iupa-ismt.ci</t>
+          <t>groupeiupaismt@gmail.com</t>
         </is>
       </c>
       <c r="G26" s="18" t="inlineStr"/>
@@ -2423,7 +2419,7 @@
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>iupayop@iupa-ismt.ci</t>
+          <t>groupeiupaismt@gmail.com</t>
         </is>
       </c>
       <c r="G27" s="18" t="inlineStr"/>
@@ -2799,7 +2795,7 @@
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>plateau@groupeaist.net</t>
+          <t>aistplateau@gmail.com</t>
         </is>
       </c>
       <c r="G35" s="18" t="inlineStr"/>
@@ -2846,11 +2842,7 @@
           <t>+225 27 21 24 12 18</t>
         </is>
       </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>treichville@groupeaist.net</t>
-        </is>
-      </c>
+      <c r="F36" s="17" t="inlineStr"/>
       <c r="G36" s="18" t="inlineStr"/>
       <c r="H36" s="18" t="inlineStr"/>
       <c r="I36" s="18" t="inlineStr">
@@ -2942,7 +2934,7 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>cesa-plateau@cofecesa.net</t>
+          <t>cofecesa@cofecesa.net</t>
         </is>
       </c>
       <c r="G38" s="18" t="inlineStr"/>
@@ -3973,7 +3965,7 @@
       </c>
       <c r="F61" s="17" t="inlineStr">
         <is>
-          <t>esc-abidjan@gmail.com</t>
+          <t>info@esc-abj-bke.net</t>
         </is>
       </c>
       <c r="G61" s="18" t="inlineStr"/>
@@ -4255,7 +4247,7 @@
       </c>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>info@groupehetec.com</t>
+          <t>info@groupehetec.net</t>
         </is>
       </c>
       <c r="G67" s="18" t="inlineStr"/>
@@ -4654,11 +4646,7 @@
       </c>
       <c r="D76" s="17" t="inlineStr"/>
       <c r="E76" s="17" t="inlineStr"/>
-      <c r="F76" s="17" t="inlineStr">
-        <is>
-          <t>contact@isacm.ci</t>
-        </is>
-      </c>
+      <c r="F76" s="17" t="inlineStr"/>
       <c r="G76" s="18" t="inlineStr"/>
       <c r="H76" s="18" t="inlineStr"/>
       <c r="I76" s="18" t="inlineStr">
@@ -4793,11 +4781,7 @@
           <t>+225 07 08 11 86 87</t>
         </is>
       </c>
-      <c r="F79" s="17" t="inlineStr">
-        <is>
-          <t>info@ita-education.ci</t>
-        </is>
-      </c>
+      <c r="F79" s="17" t="inlineStr"/>
       <c r="G79" s="18" t="inlineStr"/>
       <c r="H79" s="18" t="inlineStr"/>
       <c r="I79" s="18" t="inlineStr">
@@ -4838,11 +4822,7 @@
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr"/>
-      <c r="F80" s="17" t="inlineStr">
-        <is>
-          <t>infos@ites.ci</t>
-        </is>
-      </c>
+      <c r="F80" s="17" t="inlineStr"/>
       <c r="G80" s="18" t="inlineStr"/>
       <c r="H80" s="18" t="inlineStr"/>
       <c r="I80" s="18" t="inlineStr">
@@ -5216,7 +5196,7 @@
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>info@uigb.org</t>
+          <t>admissions@iugb.edu.ci</t>
         </is>
       </c>
       <c r="G88" s="18" t="inlineStr"/>
@@ -5811,11 +5791,7 @@
         </is>
       </c>
       <c r="E101" s="17" t="inlineStr"/>
-      <c r="F101" s="17" t="inlineStr">
-        <is>
-          <t>lyceetechniqueabidjan@yahoo.fr</t>
-        </is>
-      </c>
+      <c r="F101" s="17" t="inlineStr"/>
       <c r="G101" s="18" t="inlineStr"/>
       <c r="H101" s="18" t="inlineStr"/>
       <c r="I101" s="18" t="inlineStr">
@@ -6129,7 +6105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:O106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6145,6 +6121,8 @@
     <col width="32" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6211,6 +6189,16 @@
       <c r="M1" s="12" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="N1" s="12" t="inlineStr">
+        <is>
+          <t>Type email</t>
+        </is>
+      </c>
+      <c r="O1" s="12" t="inlineStr">
+        <is>
+          <t>Etat email</t>
         </is>
       </c>
     </row>
@@ -6264,6 +6252,12 @@
           <t>AnnuaireCI</t>
         </is>
       </c>
+      <c r="N2" s="21" t="inlineStr"/>
+      <c r="O2" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -6317,6 +6311,12 @@
       <c r="M3" s="21" t="inlineStr">
         <is>
           <t>edukiya.com</t>
+        </is>
+      </c>
+      <c r="N3" s="21" t="inlineStr"/>
+      <c r="O3" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -6374,6 +6374,12 @@
           <t>UPESUP</t>
         </is>
       </c>
+      <c r="N4" s="21" t="inlineStr"/>
+      <c r="O4" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
@@ -6429,6 +6435,12 @@
           <t>Le Grand Frere</t>
         </is>
       </c>
+      <c r="N5" s="21" t="inlineStr"/>
+      <c r="O5" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
@@ -6471,11 +6483,7 @@
           <t>+225 07 59 74 39 10</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
-        <is>
-          <t>infos24@gestpci.com</t>
-        </is>
-      </c>
+      <c r="I6" s="21" t="inlineStr"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t>gestpci.com</t>
@@ -6486,7 +6494,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -6494,6 +6502,12 @@
       <c r="M6" s="21" t="inlineStr">
         <is>
           <t>Site officiel gestpci.com</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="inlineStr"/>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6554,7 @@
       </c>
       <c r="I7" s="21" t="inlineStr">
         <is>
-          <t>info@groupehetec.com</t>
+          <t>info@groupehetec.net</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -6560,7 +6574,17 @@
       </c>
       <c r="M7" s="21" t="inlineStr">
         <is>
-          <t>Le Grand Frere + Annuaire Pratik</t>
+          <t>Le Grand Frere + Annuaire Pratik | email : Le Grand Frere + Edukiya - domaine .net en service</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O7" s="24" t="inlineStr">
+        <is>
+          <t>a verifier</t>
         </is>
       </c>
     </row>
@@ -6618,6 +6642,12 @@
           <t>CiTrade</t>
         </is>
       </c>
+      <c r="N8" s="21" t="inlineStr"/>
+      <c r="O8" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
@@ -6658,7 +6688,7 @@
       <c r="H9" s="21" t="inlineStr"/>
       <c r="I9" s="21" t="inlineStr">
         <is>
-          <t>infos@isfmi.net</t>
+          <t>isfmiisfmi@yahoo.fr</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -6671,14 +6701,24 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L9" s="22" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
         <is>
-          <t>Site officiel isfmi.net</t>
+          <t>Site officiel isfmi.net | email : etudes.ci + Le Grand Frere</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O9" s="24" t="inlineStr">
+        <is>
+          <t>a verifier</t>
         </is>
       </c>
     </row>
@@ -6746,6 +6786,16 @@
       <c r="M10" s="21" t="inlineStr">
         <is>
           <t>Site officiel + AnnuaireCI</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O10" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -6807,6 +6857,16 @@
           <t>Page contact insaac.edu.ci</t>
         </is>
       </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O11" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
@@ -6870,6 +6930,16 @@
           <t>ipnetp.ci + AnnuaireCI</t>
         </is>
       </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O12" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="inlineStr">
@@ -6933,6 +7003,16 @@
           <t>Site officiel istcpolytechnique.ci</t>
         </is>
       </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O13" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
@@ -6996,6 +7076,16 @@
           <t>simplon.ci</t>
         </is>
       </c>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O14" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="21" t="inlineStr">
@@ -7049,7 +7139,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L15" s="22" t="inlineStr">
+      <c r="L15" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -7057,6 +7147,16 @@
       <c r="M15" s="21" t="inlineStr">
         <is>
           <t>Site officiel ucaouua.com</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O15" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7203,7 @@
       </c>
       <c r="I16" s="21" t="inlineStr">
         <is>
-          <t>esc-abidjan@gmail.com</t>
+          <t>info@esc-abj-bke.net</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -7123,7 +7223,17 @@
       </c>
       <c r="M16" s="21" t="inlineStr">
         <is>
-          <t>AnnuaireCI + alloecole.ci</t>
+          <t>AnnuaireCI + alloecole.ci | email : AnnuaireCI</t>
+        </is>
+      </c>
+      <c r="N16" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O16" s="24" t="inlineStr">
+        <is>
+          <t>a verifier</t>
         </is>
       </c>
     </row>
@@ -7181,6 +7291,12 @@
           <t>UPESUP</t>
         </is>
       </c>
+      <c r="N17" s="21" t="inlineStr"/>
+      <c r="O17" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="21" t="inlineStr">
@@ -7236,6 +7352,12 @@
           <t>UPESUP</t>
         </is>
       </c>
+      <c r="N18" s="21" t="inlineStr"/>
+      <c r="O18" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="inlineStr">
@@ -7285,7 +7407,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L19" s="22" t="inlineStr">
+      <c r="L19" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -7293,6 +7415,16 @@
       <c r="M19" s="21" t="inlineStr">
         <is>
           <t>Site officiel iisan-abidjan.com</t>
+        </is>
+      </c>
+      <c r="N19" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O19" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7480,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L20" s="22" t="inlineStr">
+      <c r="L20" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -7356,6 +7488,16 @@
       <c r="M20" s="21" t="inlineStr">
         <is>
           <t>Site officiel neurones-academy.com</t>
+        </is>
+      </c>
+      <c r="N20" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O20" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -7417,6 +7559,12 @@
           <t>institutboosterafrique.com</t>
         </is>
       </c>
+      <c r="N21" s="21" t="inlineStr"/>
+      <c r="O21" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
@@ -7476,6 +7624,16 @@
           <t>Le Grand Frere</t>
         </is>
       </c>
+      <c r="N22" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O22" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
@@ -7529,7 +7687,7 @@
           <t>Directeur des Etudes (par campus)</t>
         </is>
       </c>
-      <c r="L23" s="22" t="inlineStr">
+      <c r="L23" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -7537,6 +7695,16 @@
       <c r="M23" s="21" t="inlineStr">
         <is>
           <t>Site officiel eipc-abidjan.ci</t>
+        </is>
+      </c>
+      <c r="N23" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O23" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7764,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L24" s="22" t="inlineStr">
+      <c r="L24" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -7604,6 +7772,16 @@
       <c r="M24" s="21" t="inlineStr">
         <is>
           <t>Page contact ifsm.ci</t>
+        </is>
+      </c>
+      <c r="N24" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O24" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -7661,6 +7839,16 @@
           <t>Page officielle Africa Digital Academy</t>
         </is>
       </c>
+      <c r="N25" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O25" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
@@ -7720,6 +7908,12 @@
           <t>AnnuaireCI + ensit.ci</t>
         </is>
       </c>
+      <c r="N26" s="21" t="inlineStr"/>
+      <c r="O26" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
@@ -7779,6 +7973,12 @@
           <t>Le Grand Frere</t>
         </is>
       </c>
+      <c r="N27" s="21" t="inlineStr"/>
+      <c r="O27" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
@@ -7817,11 +8017,7 @@
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr"/>
-      <c r="I28" s="21" t="inlineStr">
-        <is>
-          <t>info@geige.ci</t>
-        </is>
-      </c>
+      <c r="I28" s="21" t="inlineStr"/>
       <c r="J28" s="21" t="inlineStr">
         <is>
           <t>geige.ci</t>
@@ -7832,7 +8028,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L28" s="22" t="inlineStr">
+      <c r="L28" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -7840,6 +8036,12 @@
       <c r="M28" s="21" t="inlineStr">
         <is>
           <t>Site officiel geige.ci</t>
+        </is>
+      </c>
+      <c r="N28" s="21" t="inlineStr"/>
+      <c r="O28" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -7897,6 +8099,12 @@
           <t>UPESUP</t>
         </is>
       </c>
+      <c r="N29" s="21" t="inlineStr"/>
+      <c r="O29" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
@@ -7952,6 +8160,16 @@
           <t>supmanagement.ma</t>
         </is>
       </c>
+      <c r="N30" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O30" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="21" t="inlineStr">
@@ -8011,6 +8229,16 @@
           <t>Le Grand Frere</t>
         </is>
       </c>
+      <c r="N31" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O31" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="21" t="inlineStr">
@@ -8068,7 +8296,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L32" s="22" t="inlineStr">
+      <c r="L32" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -8076,6 +8304,16 @@
       <c r="M32" s="21" t="inlineStr">
         <is>
           <t>Page contact officielle iuaci.org</t>
+        </is>
+      </c>
+      <c r="N32" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O32" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -8112,11 +8350,7 @@
       </c>
       <c r="G33" s="21" t="inlineStr"/>
       <c r="H33" s="21" t="inlineStr"/>
-      <c r="I33" s="21" t="inlineStr">
-        <is>
-          <t>infos@ites.ci</t>
-        </is>
-      </c>
+      <c r="I33" s="21" t="inlineStr"/>
       <c r="J33" s="21" t="inlineStr">
         <is>
           <t>www.ites.ci</t>
@@ -8135,6 +8369,12 @@
       <c r="M33" s="21" t="inlineStr">
         <is>
           <t>ites.ci + AnnuaireCI</t>
+        </is>
+      </c>
+      <c r="N33" s="21" t="inlineStr"/>
+      <c r="O33" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8430,7 @@
           <t>Directeur des Etudes (par campus)</t>
         </is>
       </c>
-      <c r="L34" s="22" t="inlineStr">
+      <c r="L34" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -8198,6 +8438,16 @@
       <c r="M34" s="21" t="inlineStr">
         <is>
           <t>Site officiel esma-edu.com</t>
+        </is>
+      </c>
+      <c r="N34" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O34" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -8263,6 +8513,16 @@
           <t>AnnuaireCI</t>
         </is>
       </c>
+      <c r="N35" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O35" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
@@ -8316,7 +8576,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L36" s="22" t="inlineStr">
+      <c r="L36" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -8324,6 +8584,16 @@
       <c r="M36" s="21" t="inlineStr">
         <is>
           <t>Site officiel cup-ci.org</t>
+        </is>
+      </c>
+      <c r="N36" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O36" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8653,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L37" s="22" t="inlineStr">
+      <c r="L37" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -8391,6 +8661,16 @@
       <c r="M37" s="21" t="inlineStr">
         <is>
           <t>Page contact officielle groupecsi-pp.com</t>
+        </is>
+      </c>
+      <c r="N37" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O37" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8705,7 @@
       <c r="H38" s="21" t="inlineStr"/>
       <c r="I38" s="21" t="inlineStr">
         <is>
-          <t>iupacocody@iupa-ismt.ci</t>
+          <t>groupeiupaismt@gmail.com</t>
         </is>
       </c>
       <c r="J38" s="21" t="inlineStr">
@@ -8438,14 +8718,24 @@
           <t>Directeur des Etudes (par campus)</t>
         </is>
       </c>
-      <c r="L38" s="22" t="inlineStr">
+      <c r="L38" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
       <c r="M38" s="21" t="inlineStr">
         <is>
-          <t>Site officiel iupa-ismt.ci</t>
+          <t>Site officiel iupa-ismt.ci | email : Page contact officielle iupa-ismt.ci</t>
+        </is>
+      </c>
+      <c r="N38" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O38" s="24" t="inlineStr">
+        <is>
+          <t>a verifier</t>
         </is>
       </c>
     </row>
@@ -8497,7 +8787,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L39" s="22" t="inlineStr">
+      <c r="L39" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -8505,6 +8795,12 @@
       <c r="M39" s="21" t="inlineStr">
         <is>
           <t>Site officiel uist.ci</t>
+        </is>
+      </c>
+      <c r="N39" s="21" t="inlineStr"/>
+      <c r="O39" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8848,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L40" s="22" t="inlineStr">
+      <c r="L40" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -8560,6 +8856,16 @@
       <c r="M40" s="21" t="inlineStr">
         <is>
           <t>Site officiel epitech.africa</t>
+        </is>
+      </c>
+      <c r="N40" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O40" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8925,7 @@
           <t>Directeur des Etudes / Directeur Pedagogique</t>
         </is>
       </c>
-      <c r="L41" s="22" t="inlineStr">
+      <c r="L41" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -8627,6 +8933,16 @@
       <c r="M41" s="21" t="inlineStr">
         <is>
           <t>Site officiel + AnnuaireCI</t>
+        </is>
+      </c>
+      <c r="N41" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O41" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -8680,6 +8996,12 @@
           <t>UPESUP</t>
         </is>
       </c>
+      <c r="N42" s="21" t="inlineStr"/>
+      <c r="O42" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
@@ -8743,6 +9065,16 @@
           <t>uatlantique.org + AnnuaireCI</t>
         </is>
       </c>
+      <c r="N43" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O43" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="inlineStr">
@@ -8808,6 +9140,16 @@
       <c r="M44" s="21" t="inlineStr">
         <is>
           <t>groupecerco.com + AnnuaireCI</t>
+        </is>
+      </c>
+      <c r="N44" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O44" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -8867,6 +9209,12 @@
       <c r="M45" s="21" t="inlineStr">
         <is>
           <t>Le Grand Frere + UPESUP</t>
+        </is>
+      </c>
+      <c r="N45" s="21" t="inlineStr"/>
+      <c r="O45" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -8916,6 +9264,12 @@
           <t>AnnuaireCI</t>
         </is>
       </c>
+      <c r="N46" s="21" t="inlineStr"/>
+      <c r="O46" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="21" t="inlineStr">
@@ -8969,7 +9323,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L47" s="22" t="inlineStr">
+      <c r="L47" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -8977,6 +9331,16 @@
       <c r="M47" s="21" t="inlineStr">
         <is>
           <t>Site officiel ecg.ci</t>
+        </is>
+      </c>
+      <c r="N47" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O47" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9392,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L48" s="22" t="inlineStr">
+      <c r="L48" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -9036,6 +9400,12 @@
       <c r="M48" s="21" t="inlineStr">
         <is>
           <t>Site officiel eurof.org</t>
+        </is>
+      </c>
+      <c r="N48" s="21" t="inlineStr"/>
+      <c r="O48" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -9076,11 +9446,7 @@
         </is>
       </c>
       <c r="H49" s="21" t="inlineStr"/>
-      <c r="I49" s="21" t="inlineStr">
-        <is>
-          <t>info@ita-education.ci</t>
-        </is>
-      </c>
+      <c r="I49" s="21" t="inlineStr"/>
       <c r="J49" s="21" t="inlineStr">
         <is>
           <t>ita-education.ci</t>
@@ -9099,6 +9465,12 @@
       <c r="M49" s="21" t="inlineStr">
         <is>
           <t>AnnuaireCI + Le Grand Frere</t>
+        </is>
+      </c>
+      <c r="N49" s="21" t="inlineStr"/>
+      <c r="O49" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -9162,6 +9534,16 @@
       <c r="M50" s="21" t="inlineStr">
         <is>
           <t>groupeloko.online + AnnuaireCI</t>
+        </is>
+      </c>
+      <c r="N50" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O50" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -9219,6 +9601,12 @@
           <t>Annuaire Pratik</t>
         </is>
       </c>
+      <c r="N51" s="21" t="inlineStr"/>
+      <c r="O51" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="21" t="inlineStr">
@@ -9259,7 +9647,7 @@
       <c r="H52" s="21" t="inlineStr"/>
       <c r="I52" s="21" t="inlineStr">
         <is>
-          <t>plateau@groupeaist.net</t>
+          <t>aistplateau@gmail.com</t>
         </is>
       </c>
       <c r="J52" s="21" t="inlineStr">
@@ -9279,7 +9667,17 @@
       </c>
       <c r="M52" s="21" t="inlineStr">
         <is>
-          <t>Le Grand Frere + UPESUP</t>
+          <t>Le Grand Frere + UPESUP | email : Le Grand Frere + UPESUP</t>
+        </is>
+      </c>
+      <c r="N52" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O52" s="24" t="inlineStr">
+        <is>
+          <t>a verifier</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9720,7 @@
       <c r="H53" s="21" t="inlineStr"/>
       <c r="I53" s="21" t="inlineStr">
         <is>
-          <t>cesa-plateau@cofecesa.net</t>
+          <t>cofecesa@cofecesa.net</t>
         </is>
       </c>
       <c r="J53" s="21" t="inlineStr">
@@ -9342,7 +9740,17 @@
       </c>
       <c r="M53" s="21" t="inlineStr">
         <is>
-          <t>AnnuaireCI + UPESUP</t>
+          <t>AnnuaireCI + UPESUP | email : cofecesa.net - boite generale du groupe, repli alain_achi@yahoo.fr</t>
+        </is>
+      </c>
+      <c r="N53" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O53" s="24" t="inlineStr">
+        <is>
+          <t>a verifier</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9806,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L54" s="22" t="inlineStr">
+      <c r="L54" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -9406,6 +9814,16 @@
       <c r="M54" s="21" t="inlineStr">
         <is>
           <t>Site officiel esccastaing.com</t>
+        </is>
+      </c>
+      <c r="N54" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O54" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -9471,6 +9889,12 @@
           <t>AnnuaireCI + esicom.info</t>
         </is>
       </c>
+      <c r="N55" s="21" t="inlineStr"/>
+      <c r="O55" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="21" t="inlineStr">
@@ -9528,7 +9952,7 @@
           <t>Directeur des Etudes (par campus)</t>
         </is>
       </c>
-      <c r="L56" s="22" t="inlineStr">
+      <c r="L56" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -9536,6 +9960,16 @@
       <c r="M56" s="21" t="inlineStr">
         <is>
           <t>Page contact esbtp-ci.net</t>
+        </is>
+      </c>
+      <c r="N56" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O56" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -9595,7 +10029,7 @@
           <t>Directeur des Etudes (par campus)</t>
         </is>
       </c>
-      <c r="L57" s="22" t="inlineStr">
+      <c r="L57" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -9603,6 +10037,16 @@
       <c r="M57" s="21" t="inlineStr">
         <is>
           <t>Site officiel pigierci.com</t>
+        </is>
+      </c>
+      <c r="N57" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O57" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -9660,6 +10104,12 @@
           <t>AnnuaireCI + Le Grand Frere</t>
         </is>
       </c>
+      <c r="N58" s="21" t="inlineStr"/>
+      <c r="O58" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="21" t="inlineStr">
@@ -9723,6 +10173,16 @@
           <t>AnnuaireCI + groupescoget.com</t>
         </is>
       </c>
+      <c r="N59" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O59" s="25" t="inlineStr">
+        <is>
+          <t>boite pleine</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="21" t="inlineStr">
@@ -9782,6 +10242,16 @@
           <t>AnnuaireCI + Le Grand Frere</t>
         </is>
       </c>
+      <c r="N60" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O60" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="21" t="inlineStr">
@@ -9820,11 +10290,7 @@
         </is>
       </c>
       <c r="H61" s="21" t="inlineStr"/>
-      <c r="I61" s="21" t="inlineStr">
-        <is>
-          <t>treichville@groupeaist.net</t>
-        </is>
-      </c>
+      <c r="I61" s="21" t="inlineStr"/>
       <c r="J61" s="21" t="inlineStr">
         <is>
           <t>groupeaist.com</t>
@@ -9843,6 +10309,12 @@
       <c r="M61" s="21" t="inlineStr">
         <is>
           <t>AnnuaireCI + UPESUP</t>
+        </is>
+      </c>
+      <c r="N61" s="21" t="inlineStr"/>
+      <c r="O61" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -9902,6 +10374,12 @@
       <c r="M62" s="21" t="inlineStr">
         <is>
           <t>Site officiel esatic.ci</t>
+        </is>
+      </c>
+      <c r="N62" s="21" t="inlineStr"/>
+      <c r="O62" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -9955,6 +10433,12 @@
           <t>Le Grand Frere</t>
         </is>
       </c>
+      <c r="N63" s="21" t="inlineStr"/>
+      <c r="O63" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="21" t="inlineStr">
@@ -10010,6 +10494,12 @@
           <t>GoAfricaOnline</t>
         </is>
       </c>
+      <c r="N64" s="21" t="inlineStr"/>
+      <c r="O64" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="21" t="inlineStr">
@@ -10071,6 +10561,12 @@
       <c r="M65" s="21" t="inlineStr">
         <is>
           <t>Le Grand Frere</t>
+        </is>
+      </c>
+      <c r="N65" s="21" t="inlineStr"/>
+      <c r="O65" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -10128,6 +10624,12 @@
           <t>UPESUP</t>
         </is>
       </c>
+      <c r="N66" s="21" t="inlineStr"/>
+      <c r="O66" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="21" t="inlineStr">
@@ -10172,7 +10674,7 @@
       </c>
       <c r="I67" s="21" t="inlineStr">
         <is>
-          <t>iupayop@iupa-ismt.ci</t>
+          <t>groupeiupaismt@gmail.com</t>
         </is>
       </c>
       <c r="J67" s="21" t="inlineStr">
@@ -10185,14 +10687,24 @@
           <t>Directeur des Etudes (par campus)</t>
         </is>
       </c>
-      <c r="L67" s="22" t="inlineStr">
+      <c r="L67" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
       <c r="M67" s="21" t="inlineStr">
         <is>
-          <t>Site officiel iupa-ismt.ci</t>
+          <t>Site officiel iupa-ismt.ci | email : Page contact officielle iupa-ismt.ci</t>
+        </is>
+      </c>
+      <c r="N67" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O67" s="24" t="inlineStr">
+        <is>
+          <t>a verifier</t>
         </is>
       </c>
     </row>
@@ -10246,6 +10758,12 @@
           <t>AnnuaireCI + Abidjan.net Pages Jaunes</t>
         </is>
       </c>
+      <c r="N68" s="21" t="inlineStr"/>
+      <c r="O68" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="21" t="inlineStr">
@@ -10297,6 +10815,12 @@
           <t>annuaire cartographique en ligne</t>
         </is>
       </c>
+      <c r="N69" s="21" t="inlineStr"/>
+      <c r="O69" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="21" t="inlineStr">
@@ -10346,7 +10870,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L70" s="22" t="inlineStr">
+      <c r="L70" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -10354,6 +10878,16 @@
       <c r="M70" s="21" t="inlineStr">
         <is>
           <t>univ-na.ci / alluniversity.info</t>
+        </is>
+      </c>
+      <c r="N70" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O70" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10943,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L71" s="22" t="inlineStr">
+      <c r="L71" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -10417,6 +10951,16 @@
       <c r="M71" s="21" t="inlineStr">
         <is>
           <t>bem.ci</t>
+        </is>
+      </c>
+      <c r="N71" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O71" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -10478,6 +11022,16 @@
           <t>legrandfrere.africa</t>
         </is>
       </c>
+      <c r="N72" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O72" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="21" t="inlineStr">
@@ -10527,7 +11081,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L73" s="22" t="inlineStr">
+      <c r="L73" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -10535,6 +11089,16 @@
       <c r="M73" s="21" t="inlineStr">
         <is>
           <t>egt.ci</t>
+        </is>
+      </c>
+      <c r="N73" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O73" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -10596,6 +11160,16 @@
           <t>annuaireci.com</t>
         </is>
       </c>
+      <c r="N74" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O74" s="25" t="inlineStr">
+        <is>
+          <t>boite pleine</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="21" t="inlineStr">
@@ -10649,7 +11223,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L75" s="22" t="inlineStr">
+      <c r="L75" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -10657,6 +11231,16 @@
       <c r="M75" s="21" t="inlineStr">
         <is>
           <t>isaeci.com</t>
+        </is>
+      </c>
+      <c r="N75" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O75" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -10714,6 +11298,12 @@
           <t>edukiya.com</t>
         </is>
       </c>
+      <c r="N76" s="21" t="inlineStr"/>
+      <c r="O76" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="21" t="inlineStr">
@@ -10748,11 +11338,7 @@
       </c>
       <c r="G77" s="21" t="inlineStr"/>
       <c r="H77" s="21" t="inlineStr"/>
-      <c r="I77" s="21" t="inlineStr">
-        <is>
-          <t>lyceetechniqueabidjan@yahoo.fr</t>
-        </is>
-      </c>
+      <c r="I77" s="21" t="inlineStr"/>
       <c r="J77" s="21" t="inlineStr">
         <is>
           <t>lta-ci.net</t>
@@ -10763,7 +11349,7 @@
           <t>Proviseur / Censeur</t>
         </is>
       </c>
-      <c r="L77" s="22" t="inlineStr">
+      <c r="L77" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -10771,6 +11357,12 @@
       <c r="M77" s="21" t="inlineStr">
         <is>
           <t>lta-ci.net</t>
+        </is>
+      </c>
+      <c r="N77" s="21" t="inlineStr"/>
+      <c r="O77" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -10828,6 +11420,12 @@
           <t>annuaireci.com / upesup.ci</t>
         </is>
       </c>
+      <c r="N78" s="21" t="inlineStr"/>
+      <c r="O78" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="21" t="inlineStr">
@@ -10877,7 +11475,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L79" s="22" t="inlineStr">
+      <c r="L79" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -10885,6 +11483,12 @@
       <c r="M79" s="21" t="inlineStr">
         <is>
           <t>umeci.org.ci / upesup.ci</t>
+        </is>
+      </c>
+      <c r="N79" s="21" t="inlineStr"/>
+      <c r="O79" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -10932,7 +11536,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L80" s="22" t="inlineStr">
+      <c r="L80" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -10940,6 +11544,16 @@
       <c r="M80" s="21" t="inlineStr">
         <is>
           <t>uvci.edu.ci</t>
+        </is>
+      </c>
+      <c r="N80" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O80" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -10995,7 +11609,7 @@
           <t>Proviseur / Censeur</t>
         </is>
       </c>
-      <c r="L81" s="22" t="inlineStr">
+      <c r="L81" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -11003,6 +11617,16 @@
       <c r="M81" s="21" t="inlineStr">
         <is>
           <t>lyceeprohotelier.sch-ci.org / lphr.ci</t>
+        </is>
+      </c>
+      <c r="N81" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O81" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -11060,6 +11684,12 @@
           <t>agefop.ci / annuaireci.com</t>
         </is>
       </c>
+      <c r="N82" s="21" t="inlineStr"/>
+      <c r="O82" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="21" t="inlineStr">
@@ -11115,6 +11745,12 @@
           <t>emploi.ci / excelafrica.com</t>
         </is>
       </c>
+      <c r="N83" s="21" t="inlineStr"/>
+      <c r="O83" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="21" t="inlineStr">
@@ -11168,7 +11804,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L84" s="22" t="inlineStr">
+      <c r="L84" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -11176,6 +11812,16 @@
       <c r="M84" s="21" t="inlineStr">
         <is>
           <t>arstm.net</t>
+        </is>
+      </c>
+      <c r="N84" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O84" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -11231,7 +11877,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L85" s="22" t="inlineStr">
+      <c r="L85" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -11239,6 +11885,16 @@
       <c r="M85" s="21" t="inlineStr">
         <is>
           <t>cfomis-ci.com</t>
+        </is>
+      </c>
+      <c r="N85" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O85" s="25" t="inlineStr">
+        <is>
+          <t>boite pleine</t>
         </is>
       </c>
     </row>
@@ -11279,11 +11935,7 @@
         </is>
       </c>
       <c r="H86" s="21" t="inlineStr"/>
-      <c r="I86" s="21" t="inlineStr">
-        <is>
-          <t>contact@groupelasorbonne.com</t>
-        </is>
-      </c>
+      <c r="I86" s="21" t="inlineStr"/>
       <c r="J86" s="21" t="inlineStr">
         <is>
           <t>groupelasorbonne.ci</t>
@@ -11294,7 +11946,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L86" s="22" t="inlineStr">
+      <c r="L86" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -11302,6 +11954,12 @@
       <c r="M86" s="21" t="inlineStr">
         <is>
           <t>groupelasorbonne.ci / annuaireci.com</t>
+        </is>
+      </c>
+      <c r="N86" s="21" t="inlineStr"/>
+      <c r="O86" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -11357,7 +12015,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L87" s="22" t="inlineStr">
+      <c r="L87" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -11365,6 +12023,16 @@
       <c r="M87" s="21" t="inlineStr">
         <is>
           <t>esmit-ci.com</t>
+        </is>
+      </c>
+      <c r="N87" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O87" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -11416,7 +12084,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L88" s="22" t="inlineStr">
+      <c r="L88" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -11424,6 +12092,12 @@
       <c r="M88" s="21" t="inlineStr">
         <is>
           <t>imghcotedivoire.ci</t>
+        </is>
+      </c>
+      <c r="N88" s="21" t="inlineStr"/>
+      <c r="O88" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -11475,7 +12149,7 @@
           <t>Proviseur / Censeur</t>
         </is>
       </c>
-      <c r="L89" s="22" t="inlineStr">
+      <c r="L89" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -11483,6 +12157,16 @@
       <c r="M89" s="21" t="inlineStr">
         <is>
           <t>lpcy.sch-ci.org / edukiya.com</t>
+        </is>
+      </c>
+      <c r="N89" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O89" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -11534,7 +12218,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L90" s="22" t="inlineStr">
+      <c r="L90" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -11542,6 +12226,16 @@
       <c r="M90" s="21" t="inlineStr">
         <is>
           <t>univ-ao.edu.ci</t>
+        </is>
+      </c>
+      <c r="N90" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O90" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -11595,6 +12289,12 @@
           <t>AnnuaireCI + CiTrade</t>
         </is>
       </c>
+      <c r="N91" s="21" t="inlineStr"/>
+      <c r="O91" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="21" t="inlineStr">
@@ -11644,7 +12344,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L92" s="22" t="inlineStr">
+      <c r="L92" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -11652,6 +12352,16 @@
       <c r="M92" s="21" t="inlineStr">
         <is>
           <t>ujlog.edu.ci</t>
+        </is>
+      </c>
+      <c r="N92" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O92" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -11709,6 +12419,12 @@
           <t>edukiya.com</t>
         </is>
       </c>
+      <c r="N93" s="21" t="inlineStr"/>
+      <c r="O93" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="21" t="inlineStr">
@@ -11758,7 +12474,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L94" s="22" t="inlineStr">
+      <c r="L94" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -11766,6 +12482,16 @@
       <c r="M94" s="21" t="inlineStr">
         <is>
           <t>Site officiel iit.ci</t>
+        </is>
+      </c>
+      <c r="N94" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O94" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -11808,7 +12534,7 @@
       <c r="H95" s="21" t="inlineStr"/>
       <c r="I95" s="21" t="inlineStr">
         <is>
-          <t>info@uigb.org</t>
+          <t>admissions@iugb.edu.ci</t>
         </is>
       </c>
       <c r="J95" s="21" t="inlineStr">
@@ -11828,7 +12554,17 @@
       </c>
       <c r="M95" s="21" t="inlineStr">
         <is>
-          <t>uigb.net + AnnuaireCI</t>
+          <t>uigb.net + AnnuaireCI | email : iugb.edu.ci - domaine actif, uigb.org etant l'ancien</t>
+        </is>
+      </c>
+      <c r="N95" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O95" s="24" t="inlineStr">
+        <is>
+          <t>a verifier</t>
         </is>
       </c>
     </row>
@@ -11857,11 +12593,7 @@
       <c r="F96" s="21" t="inlineStr"/>
       <c r="G96" s="21" t="inlineStr"/>
       <c r="H96" s="21" t="inlineStr"/>
-      <c r="I96" s="21" t="inlineStr">
-        <is>
-          <t>contact@isacm.ci</t>
-        </is>
-      </c>
+      <c r="I96" s="21" t="inlineStr"/>
       <c r="J96" s="21" t="inlineStr">
         <is>
           <t>isacm-educ.com</t>
@@ -11872,7 +12604,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L96" s="22" t="inlineStr">
+      <c r="L96" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -11880,6 +12612,12 @@
       <c r="M96" s="21" t="inlineStr">
         <is>
           <t>Site officiel isacm-educ.com</t>
+        </is>
+      </c>
+      <c r="N96" s="21" t="inlineStr"/>
+      <c r="O96" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
         </is>
       </c>
     </row>
@@ -11941,6 +12679,12 @@
           <t>facebook.com/upgc.edu</t>
         </is>
       </c>
+      <c r="N97" s="21" t="inlineStr"/>
+      <c r="O97" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
@@ -12000,6 +12744,16 @@
           <t>esgs-ci.com</t>
         </is>
       </c>
+      <c r="N98" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O98" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="21" t="inlineStr">
@@ -12053,7 +12807,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L99" s="22" t="inlineStr">
+      <c r="L99" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -12061,6 +12815,16 @@
       <c r="M99" s="21" t="inlineStr">
         <is>
           <t>Site officiel usp.edu.ci</t>
+        </is>
+      </c>
+      <c r="N99" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O99" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -12120,6 +12884,16 @@
       <c r="M100" s="21" t="inlineStr">
         <is>
           <t>collegeheleis.com</t>
+        </is>
+      </c>
+      <c r="N100" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O100" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -12177,6 +12951,12 @@
           <t>AnnuaireCI</t>
         </is>
       </c>
+      <c r="N101" s="21" t="inlineStr"/>
+      <c r="O101" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="21" t="inlineStr">
@@ -12236,6 +13016,12 @@
           <t>AnnuaireCI</t>
         </is>
       </c>
+      <c r="N102" s="21" t="inlineStr"/>
+      <c r="O102" s="22" t="inlineStr">
+        <is>
+          <t>sans email</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="21" t="inlineStr">
@@ -12291,6 +13077,16 @@
           <t>esgs-ci.com (antenne)</t>
         </is>
       </c>
+      <c r="N103" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O103" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="21" t="inlineStr">
@@ -12340,7 +13136,7 @@
           <t>Proviseur / Censeur</t>
         </is>
       </c>
-      <c r="L104" s="22" t="inlineStr">
+      <c r="L104" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -12348,6 +13144,16 @@
       <c r="M104" s="21" t="inlineStr">
         <is>
           <t>lsy.ci</t>
+        </is>
+      </c>
+      <c r="N104" s="21" t="inlineStr">
+        <is>
+          <t>gratuite</t>
+        </is>
+      </c>
+      <c r="O104" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -12399,7 +13205,7 @@
           <t>Directeur des Etudes</t>
         </is>
       </c>
-      <c r="L105" s="22" t="inlineStr">
+      <c r="L105" s="23" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
@@ -12407,6 +13213,16 @@
       <c r="M105" s="21" t="inlineStr">
         <is>
           <t>supagro-afrique.com</t>
+        </is>
+      </c>
+      <c r="N105" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O105" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
         </is>
       </c>
     </row>
@@ -12472,9 +13288,19 @@
           <t>inphb.edu.ci</t>
         </is>
       </c>
+      <c r="N106" s="21" t="inlineStr">
+        <is>
+          <t>domaine propre</t>
+        </is>
+      </c>
+      <c r="O106" s="23" t="inlineStr">
+        <is>
+          <t>valide</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M106"/>
+  <autoFilter ref="A1:O106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12503,45 +13329,45 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Prestation de base : UNE seance de 2h par classe. La 2e seance se negocie, elle n'est jamais promise d'emblee.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>Aucun suivi individuel, aucun groupe WhatsApp : l'interlocuteur est l'etablissement, pas l'eleve.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Les deux paliers</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Montant par eleve</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>Prestation de base</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>2e seance</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="29" t="n">
         <v>5000</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -12556,7 +13382,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="29" t="n">
         <v>10000</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -12571,84 +13397,84 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Les deux montants ci-dessus sont en bleu : ce sont les seules valeurs a modifier. Le tableau ci-dessous se recalcule.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Chiffre d'affaires par classe, pour 2h de presence</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Effectif de la classe</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>A 5 000 F par eleve</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>A 10 000 F par eleve</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="31">
         <f>$B13*$B$7</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="31">
         <f>$B13*$B$8</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="31">
         <f>$B14*$B$7</f>
         <v/>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="31">
         <f>$B14*$B$8</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="31">
         <f>$B15*$B$7</f>
         <v/>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="31">
         <f>$B15*$B$8</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="31">
         <f>$B16*$B$7</f>
         <v/>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="31">
         <f>$B16*$B$8</f>
         <v/>
       </c>
@@ -12659,24 +13485,24 @@
           <t>5 classes de 40 eleves</t>
         </is>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="32">
         <f>5*40*$B$7</f>
         <v/>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="32">
         <f>5*40*$B$8</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Le volume vient du NOMBRE DE CLASSES, jamais du nombre de seances.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>Regles de negociation a tenir</t>
         </is>
@@ -12755,14 +13581,14 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>Contenu de la seance (2h)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
@@ -12774,7 +13600,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="30" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
@@ -12786,7 +13612,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>40 min</t>
         </is>
@@ -12798,7 +13624,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="30" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
@@ -12810,7 +13636,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
@@ -12822,7 +13648,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="30" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>10 min</t>
         </is>
@@ -12834,7 +13660,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>5 min</t>
         </is>
@@ -12846,14 +13672,14 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="27" t="inlineStr">
         <is>
           <t>2e seance - uniquement si negociee</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="30" t="inlineStr">
+      <c r="B39" s="33" t="inlineStr">
         <is>
           <t>35 min</t>
         </is>
@@ -12865,7 +13691,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="30" t="inlineStr">
+      <c r="B40" s="33" t="inlineStr">
         <is>
           <t>40 min</t>
         </is>
@@ -12877,7 +13703,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="30" t="inlineStr">
+      <c r="B41" s="33" t="inlineStr">
         <is>
           <t>25 min</t>
         </is>
@@ -12889,7 +13715,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="30" t="inlineStr">
+      <c r="B42" s="33" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
@@ -12901,7 +13727,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="30" t="inlineStr">
+      <c r="B44" s="33" t="inlineStr">
         <is>
           <t>Materiel demande a l'ecole : une salle, un videoprojecteur, une prise. Les eleves utilisent leur telephone.</t>
         </is>
@@ -12954,7 +13780,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>1. WhatsApp (premier contact, le plus efficace en CI)</t>
         </is>
@@ -13010,7 +13836,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>2. Appel au standard (quand on n'a que le fixe)</t>
         </is>
@@ -13038,7 +13864,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="31" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>3. E-mail (trace formelle, apres le WhatsApp)</t>
         </is>
@@ -13094,26 +13920,26 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="31" t="inlineStr">
+      <c r="B26" s="34" t="inlineStr">
         <is>
           <t>4. Objections qui reviennent</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>Objection</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t>Reponse</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>On n'a pas de salle informatique</t>
         </is>
@@ -13125,7 +13951,7 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="30" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Ce n'est pas au programme officiel</t>
         </is>
@@ -13137,7 +13963,7 @@
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>Qui paie ?</t>
         </is>
@@ -13149,7 +13975,7 @@
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
-      <c r="B31" s="30" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Une seule seance, ca suffit ?</t>
         </is>
@@ -13161,7 +13987,7 @@
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>C'est cher pour nos etudiants</t>
         </is>
@@ -13173,7 +13999,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="31" t="inlineStr">
+      <c r="B34" s="34" t="inlineStr">
         <is>
           <t>5. Rythme</t>
         </is>
